--- a/data/trans_orig/Q23_tabaco_R2-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q23_tabaco_R2-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo inicio en el consumo de tabaco fue antes de los 15 años en 2007</t>
+          <t>Población cuyo inicio en el consumo de tabaco fue antes de los 15 años en 2007 (tasa de respuesta: 86,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>57126</t>
+          <t>58342</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>82836</t>
+          <t>83195</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>49,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>57239</t>
+          <t>57823</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>81280</t>
+          <t>82115</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>36,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,67%</t>
+          <t>51,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>121475</t>
+          <t>123046</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>156105</t>
+          <t>156577</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>47,52%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>86240</t>
+          <t>85881</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>111950</t>
+          <t>110734</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>50,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,21%</t>
+          <t>65,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>79128</t>
+          <t>78293</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>103169</t>
+          <t>102585</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,33%</t>
+          <t>48,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,32%</t>
+          <t>63,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>173379</t>
+          <t>172907</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>208009</t>
+          <t>206438</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>63,13%</t>
+          <t>62,66%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>88452</t>
+          <t>87729</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>122467</t>
+          <t>124764</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>55637</t>
+          <t>54810</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>84208</t>
+          <t>83564</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>150656</t>
+          <t>151590</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>195379</t>
+          <t>195565</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,39%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>241725</t>
+          <t>239428</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>275740</t>
+          <t>276463</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>65,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>174703</t>
+          <t>175347</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>203274</t>
+          <t>204101</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,48%</t>
+          <t>67,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>78,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>427724</t>
+          <t>427538</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>472447</t>
+          <t>471513</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,64%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>75,67%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>88011</t>
+          <t>88051</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>122842</t>
+          <t>123499</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>62465</t>
+          <t>61789</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>93619</t>
+          <t>91914</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>161158</t>
+          <t>159428</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>207889</t>
+          <t>202685</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,09%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>252184</t>
+          <t>251527</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>287015</t>
+          <t>286975</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>67,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>76,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>204856</t>
+          <t>206561</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>236010</t>
+          <t>236686</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,63%</t>
+          <t>69,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>465613</t>
+          <t>470817</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>512344</t>
+          <t>514074</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>69,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>76,33%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>93363</t>
+          <t>93950</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>129056</t>
+          <t>129427</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24460</t>
+          <t>25636</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45923</t>
+          <t>47356</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>124607</t>
+          <t>126635</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>167858</t>
+          <t>168525</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>32,99%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>192151</t>
+          <t>191780</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>227844</t>
+          <t>227257</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,82%</t>
+          <t>59,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>70,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>143665</t>
+          <t>142232</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>165128</t>
+          <t>163952</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>75,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>342937</t>
+          <t>342270</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>386188</t>
+          <t>384160</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,14%</t>
+          <t>67,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>75,21%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>81405</t>
+          <t>82707</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>112423</t>
+          <t>112470</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>49,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2977</t>
+          <t>3009</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13833</t>
+          <t>13540</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>88264</t>
+          <t>88777</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>120917</t>
+          <t>121178</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>42,35%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>114722</t>
+          <t>114675</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>145740</t>
+          <t>144438</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>50,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>64,16%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>45186</t>
+          <t>45479</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>56042</t>
+          <t>56010</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>77,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>165248</t>
+          <t>164987</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>197901</t>
+          <t>197388</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>57,75%</t>
+          <t>57,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>68,98%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>46998</t>
+          <t>46918</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>68976</t>
+          <t>69832</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>47,71%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3754</t>
+          <t>4972</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>47884</t>
+          <t>47189</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>71980</t>
+          <t>71152</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>43,74%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>75586</t>
+          <t>74730</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>97564</t>
+          <t>97644</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>51,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>67,49%</t>
+          <t>67,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>14337</t>
+          <t>13119</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>72,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>90673</t>
+          <t>91501</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>114769</t>
+          <t>115464</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>55,75%</t>
+          <t>56,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>70,99%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>51848</t>
+          <t>50911</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>73036</t>
+          <t>71663</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>42,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>59,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1225</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8160</t>
+          <t>9326</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>67,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>54438</t>
+          <t>55325</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>77386</t>
+          <t>78151</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,87%</t>
+          <t>58,44%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>46819</t>
+          <t>48192</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>68007</t>
+          <t>68944</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>40,21%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>57,52%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>5709</t>
+          <t>4543</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>13869</t>
+          <t>12644</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>56338</t>
+          <t>55573</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>79286</t>
+          <t>78399</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>41,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>58,63%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>568525</t>
+          <t>572225</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>647867</t>
+          <t>650850</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>236687</t>
+          <t>234941</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>292305</t>
+          <t>292311</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>816937</t>
+          <t>820550</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>916984</t>
+          <t>919160</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>33,8%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1073197</t>
+          <t>1070214</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1152539</t>
+          <t>1148839</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>62,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>66,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>706059</t>
+          <t>706053</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>761677</t>
+          <t>763423</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>76,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1802443</t>
+          <t>1800267</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1902490</t>
+          <t>1898877</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>66,28%</t>
+          <t>66,2%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>69,83%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo inicio en el consumo de tabaco fue antes de los 15 años en 2012</t>
+          <t>Población cuyo inicio en el consumo de tabaco fue antes de los 15 años en 2012 (tasa de respuesta: 94,28%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>55745</t>
+          <t>55811</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>80497</t>
+          <t>81084</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>52,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>70188</t>
+          <t>69328</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>94342</t>
+          <t>94491</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>44,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>60,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>134024</t>
+          <t>134491</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>169534</t>
+          <t>169599</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>43,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>54,55%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>75341</t>
+          <t>74754</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>100093</t>
+          <t>100027</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>47,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>64,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>60726</t>
+          <t>60577</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>84880</t>
+          <t>85740</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,74%</t>
+          <t>55,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>141372</t>
+          <t>141307</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>176882</t>
+          <t>176415</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>45,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>56,89%</t>
+          <t>56,74%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>87242</t>
+          <t>87127</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>121557</t>
+          <t>122886</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>64760</t>
+          <t>65494</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>98110</t>
+          <t>97799</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>164124</t>
+          <t>163098</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>212760</t>
+          <t>211937</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,71%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>244468</t>
+          <t>243139</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>278783</t>
+          <t>278898</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,79%</t>
+          <t>66,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>76,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>225985</t>
+          <t>226296</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>259335</t>
+          <t>258601</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,73%</t>
+          <t>69,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>79,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>477359</t>
+          <t>478182</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>525995</t>
+          <t>527021</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>69,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>76,37%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>110003</t>
+          <t>111835</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>148629</t>
+          <t>147939</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>79900</t>
+          <t>78731</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>114932</t>
+          <t>114548</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>203692</t>
+          <t>201462</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>253880</t>
+          <t>254488</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,82%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>268340</t>
+          <t>269030</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>306966</t>
+          <t>305134</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>64,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>73,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>243527</t>
+          <t>243911</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>278559</t>
+          <t>279728</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>68,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>521548</t>
+          <t>520940</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>571736</t>
+          <t>573966</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>67,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>74,02%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>137885</t>
+          <t>136856</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>181755</t>
+          <t>180232</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>67871</t>
+          <t>67560</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>101538</t>
+          <t>101690</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>218552</t>
+          <t>217180</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>272351</t>
+          <t>272785</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>35,62%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>260800</t>
+          <t>262323</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>304670</t>
+          <t>305699</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>59,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,84%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>221737</t>
+          <t>221585</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>255404</t>
+          <t>255715</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,59%</t>
+          <t>68,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,01%</t>
+          <t>79,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>493479</t>
+          <t>493045</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>547278</t>
+          <t>548650</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,44%</t>
+          <t>64,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,46%</t>
+          <t>71,64%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>96479</t>
+          <t>97464</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>131088</t>
+          <t>132478</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>45,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7739</t>
+          <t>8471</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22128</t>
+          <t>23788</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>106709</t>
+          <t>109175</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>147683</t>
+          <t>148819</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,55%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>158659</t>
+          <t>157269</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>193268</t>
+          <t>192283</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>54,76%</t>
+          <t>54,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>66,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>95238</t>
+          <t>93578</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>109627</t>
+          <t>108895</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>79,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>259430</t>
+          <t>258294</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>300404</t>
+          <t>297938</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>63,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>73,18%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>71141</t>
+          <t>71586</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>101559</t>
+          <t>102573</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10849</t>
+          <t>10262</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>74475</t>
+          <t>74621</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>107540</t>
+          <t>106848</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>44,4%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>110362</t>
+          <t>109348</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>140780</t>
+          <t>140335</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>51,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>66,43%</t>
+          <t>66,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>17883</t>
+          <t>18470</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>27699</t>
+          <t>27710</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>62,24%</t>
+          <t>64,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>133113</t>
+          <t>133805</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>166178</t>
+          <t>166032</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>55,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>68,99%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>60823</t>
+          <t>61519</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>86759</t>
+          <t>87633</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>54,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>60348</t>
+          <t>60349</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>86282</t>
+          <t>88211</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>51,37%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>74528</t>
+          <t>73654</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>100464</t>
+          <t>99768</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>45,67%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>62,29%</t>
+          <t>61,86%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>8481</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>10436</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>85441</t>
+          <t>83512</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>111375</t>
+          <t>111374</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>49,76%</t>
+          <t>48,63%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>687193</t>
+          <t>689918</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>775790</t>
+          <t>780342</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>331091</t>
+          <t>331337</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>401390</t>
+          <t>402629</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1036339</t>
+          <t>1041138</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1150041</t>
+          <t>1156243</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>34,39%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1268552</t>
+          <t>1264000</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1357149</t>
+          <t>1354424</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>66,39%</t>
+          <t>66,25%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>916041</t>
+          <t>914802</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>986340</t>
+          <t>986094</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>69,53%</t>
+          <t>69,44%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>74,85%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2211732</t>
+          <t>2205530</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2325434</t>
+          <t>2320635</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>65,79%</t>
+          <t>65,61%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>69,03%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo inicio en el consumo de tabaco fue antes de los 15 años en 2016</t>
+          <t>Población cuyo inicio en el consumo de tabaco fue antes de los 15 años en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>50129</t>
+          <t>50357</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>73810</t>
+          <t>74699</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>50,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>48674</t>
+          <t>48097</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>69961</t>
+          <t>68975</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>56,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>104409</t>
+          <t>104401</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>136742</t>
+          <t>135729</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>38,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>50,26%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>74688</t>
+          <t>73799</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>98369</t>
+          <t>98141</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,3%</t>
+          <t>49,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>66,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>51568</t>
+          <t>52554</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>72855</t>
+          <t>73432</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>43,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>60,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>133286</t>
+          <t>134299</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>165619</t>
+          <t>165627</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>49,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>61,33%</t>
+          <t>61,34%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>79010</t>
+          <t>78833</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>111676</t>
+          <t>111537</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>69901</t>
+          <t>69223</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>98906</t>
+          <t>98323</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>156612</t>
+          <t>155455</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>198282</t>
+          <t>198863</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>35,11%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>191971</t>
+          <t>192110</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>224637</t>
+          <t>224814</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>63,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,98%</t>
+          <t>74,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>163781</t>
+          <t>164364</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>192786</t>
+          <t>193464</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,35%</t>
+          <t>62,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>73,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>368051</t>
+          <t>367470</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>409721</t>
+          <t>410878</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>64,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,35%</t>
+          <t>72,55%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>85411</t>
+          <t>85698</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>121504</t>
+          <t>122651</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>62855</t>
+          <t>63748</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>93696</t>
+          <t>95719</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>158515</t>
+          <t>159782</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>204948</t>
+          <t>203993</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>31,92%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>214744</t>
+          <t>213597</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>250837</t>
+          <t>250550</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,86%</t>
+          <t>63,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>209125</t>
+          <t>207102</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>239966</t>
+          <t>239073</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,06%</t>
+          <t>68,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>434121</t>
+          <t>435076</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>480554</t>
+          <t>479287</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>68,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>75,0%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>114990</t>
+          <t>114637</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>153858</t>
+          <t>154698</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>46785</t>
+          <t>47837</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>77113</t>
+          <t>76644</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>173281</t>
+          <t>173098</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>221845</t>
+          <t>220515</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>31,48%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>231513</t>
+          <t>230673</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>270381</t>
+          <t>270734</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,08%</t>
+          <t>59,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>70,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>237954</t>
+          <t>238423</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>268282</t>
+          <t>267230</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>478593</t>
+          <t>479923</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>527157</t>
+          <t>527340</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,33%</t>
+          <t>68,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,26%</t>
+          <t>75,29%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>92255</t>
+          <t>92365</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>128298</t>
+          <t>126889</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>45,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26032</t>
+          <t>26258</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>50030</t>
+          <t>50127</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>125189</t>
+          <t>123538</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>167777</t>
+          <t>167826</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>36,9%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>151666</t>
+          <t>153075</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>187709</t>
+          <t>187599</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>54,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>67,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>124769</t>
+          <t>124672</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>148767</t>
+          <t>148541</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>71,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>286985</t>
+          <t>286936</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>329573</t>
+          <t>331224</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,11%</t>
+          <t>63,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,47%</t>
+          <t>72,83%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>64944</t>
+          <t>65148</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>92987</t>
+          <t>94139</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>51,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>1039</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9600</t>
+          <t>9448</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>68939</t>
+          <t>67496</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>99738</t>
+          <t>97599</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>40,48%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>91555</t>
+          <t>90403</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>119598</t>
+          <t>119394</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>49,61%</t>
+          <t>48,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>64,81%</t>
+          <t>64,7%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>46952</t>
+          <t>47104</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>55518</t>
+          <t>55513</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>141357</t>
+          <t>143496</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>172156</t>
+          <t>173599</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>72,0%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>47768</t>
+          <t>47471</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>67746</t>
+          <t>69328</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>51,89%</t>
+          <t>53,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2292</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>47509</t>
+          <t>48252</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>68625</t>
+          <t>69431</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>49,03%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>62823</t>
+          <t>61241</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>82801</t>
+          <t>83098</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>63,42%</t>
+          <t>63,64%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>8753</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>11045</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>72989</t>
+          <t>72183</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>94105</t>
+          <t>93362</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>51,54%</t>
+          <t>50,97%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>66,45%</t>
+          <t>65,93%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>598752</t>
+          <t>598347</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>679504</t>
+          <t>681670</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>292931</t>
+          <t>291263</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>355893</t>
+          <t>356031</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>903152</t>
+          <t>904954</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1014274</t>
+          <t>1013420</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,63%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1089335</t>
+          <t>1087169</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1170087</t>
+          <t>1170492</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>61,46%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>66,15%</t>
+          <t>66,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>888607</t>
+          <t>888469</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>951569</t>
+          <t>953237</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>71,39%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>76,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1999065</t>
+          <t>1999919</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2110187</t>
+          <t>2108385</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>69,97%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo inicio en el consumo de tabaco fue antes de los 15 años en 2023</t>
+          <t>Población cuyo inicio en el consumo de tabaco fue antes de los 15 años en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19114</t>
+          <t>20598</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>55423</t>
+          <t>54966</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,77%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15553</t>
+          <t>15682</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38457</t>
+          <t>37720</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,26%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>43984</t>
+          <t>47052</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>87905</t>
+          <t>86894</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>49,45%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42208</t>
+          <t>42665</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>78517</t>
+          <t>77033</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>78,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39619</t>
+          <t>40356</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>62523</t>
+          <t>62394</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>50,74%</t>
+          <t>51,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>87803</t>
+          <t>88814</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>131724</t>
+          <t>128656</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>50,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,97%</t>
+          <t>73,22%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34535</t>
+          <t>35044</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>63539</t>
+          <t>64879</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25877</t>
+          <t>27465</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>47486</t>
+          <t>49041</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>69333</t>
+          <t>68767</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>104867</t>
+          <t>104115</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,25%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>104147</t>
+          <t>102807</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>133151</t>
+          <t>132642</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,11%</t>
+          <t>61,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>79,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>97983</t>
+          <t>96428</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>119592</t>
+          <t>118004</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,36%</t>
+          <t>66,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>81,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>208287</t>
+          <t>209039</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>243821</t>
+          <t>244387</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>66,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,86%</t>
+          <t>78,04%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47001</t>
+          <t>46702</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>74382</t>
+          <t>72553</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31381</t>
+          <t>31452</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49773</t>
+          <t>49016</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>84830</t>
+          <t>84913</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>117051</t>
+          <t>117586</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>31,3%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>114739</t>
+          <t>116568</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>142120</t>
+          <t>142419</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>60,67%</t>
+          <t>61,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>75,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>136739</t>
+          <t>137496</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>155131</t>
+          <t>155060</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>73,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>258582</t>
+          <t>258047</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>290803</t>
+          <t>290720</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,84%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>77,39%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24098</t>
+          <t>24159</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>159679</t>
+          <t>154645</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>45880</t>
+          <t>45504</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66698</t>
+          <t>66152</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>53530</t>
+          <t>57907</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>204295</t>
+          <t>205247</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,37%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>372182</t>
+          <t>377216</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>507763</t>
+          <t>507702</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>70,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>179711</t>
+          <t>180257</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>200529</t>
+          <t>200905</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,93%</t>
+          <t>73,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>573975</t>
+          <t>573023</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>724740</t>
+          <t>720363</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,75%</t>
+          <t>73,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>92,56%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>101971</t>
+          <t>103708</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>135970</t>
+          <t>136371</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>41,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>42761</t>
+          <t>44281</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>61099</t>
+          <t>62845</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>153959</t>
+          <t>153306</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>190939</t>
+          <t>190154</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>35,68%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>193161</t>
+          <t>192760</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>227160</t>
+          <t>225423</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>58,69%</t>
+          <t>58,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>68,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>142708</t>
+          <t>140962</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>161046</t>
+          <t>159526</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,02%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>78,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>341999</t>
+          <t>342784</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>378979</t>
+          <t>379632</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,17%</t>
+          <t>64,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>71,23%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>72502</t>
+          <t>73478</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>96376</t>
+          <t>96791</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>43,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15211</t>
+          <t>15354</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27438</t>
+          <t>26674</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>92889</t>
+          <t>92329</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>119613</t>
+          <t>118550</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>38,03%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>124173</t>
+          <t>123758</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>148047</t>
+          <t>147071</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>56,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>67,13%</t>
+          <t>66,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>63725</t>
+          <t>64489</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>75952</t>
+          <t>75809</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>70,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>192098</t>
+          <t>193161</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>218822</t>
+          <t>219382</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>61,63%</t>
+          <t>61,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>70,38%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>47973</t>
+          <t>48906</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>67910</t>
+          <t>67174</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>50,82%</t>
+          <t>50,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1173</t>
+          <t>1163</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6643</t>
+          <t>6593</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>51851</t>
+          <t>52219</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>71478</t>
+          <t>71545</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>45,89%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>65731</t>
+          <t>66467</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>85668</t>
+          <t>84735</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>49,74%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>64,1%</t>
+          <t>63,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>15632</t>
+          <t>15682</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>21102</t>
+          <t>21112</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>70,18%</t>
+          <t>70,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>84438</t>
+          <t>84371</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>104065</t>
+          <t>103697</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>54,16%</t>
+          <t>54,11%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>66,51%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>298145</t>
+          <t>296898</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>583493</t>
+          <t>587979</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>212404</t>
+          <t>210736</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>259085</t>
+          <t>259962</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>523840</t>
+          <t>509845</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>815602</t>
+          <t>811062</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>30,68%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1086127</t>
+          <t>1081641</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1371475</t>
+          <t>1372722</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>64,78%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>714626</t>
+          <t>713749</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>761307</t>
+          <t>762975</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1827729</t>
+          <t>1832269</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2119491</t>
+          <t>2133486</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>69,14%</t>
+          <t>69,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>80,71%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q23_tabaco_R2-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q23_tabaco_R2-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>58342</t>
+          <t>56522</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>83195</t>
+          <t>83270</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>57823</t>
+          <t>57661</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>82115</t>
+          <t>81434</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>123046</t>
+          <t>121294</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>156577</t>
+          <t>156825</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>47,6%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>85881</t>
+          <t>85806</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>110734</t>
+          <t>112554</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>50,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,49%</t>
+          <t>66,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>78293</t>
+          <t>78974</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>102585</t>
+          <t>102747</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>48,81%</t>
+          <t>49,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>64,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>172907</t>
+          <t>172659</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>206438</t>
+          <t>208190</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>52,48%</t>
+          <t>52,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>62,66%</t>
+          <t>63,19%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>87729</t>
+          <t>89552</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>124764</t>
+          <t>122872</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>54810</t>
+          <t>55067</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>83564</t>
+          <t>82555</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>151590</t>
+          <t>152493</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>195565</t>
+          <t>195456</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,37%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>239428</t>
+          <t>241320</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>276463</t>
+          <t>274640</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>66,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>75,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>175347</t>
+          <t>176356</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>204101</t>
+          <t>203844</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>68,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>78,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>427538</t>
+          <t>427647</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>471513</t>
+          <t>470610</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,61%</t>
+          <t>68,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>75,53%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>88051</t>
+          <t>88670</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>123499</t>
+          <t>123373</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>61789</t>
+          <t>62663</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>91914</t>
+          <t>93450</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>159428</t>
+          <t>159804</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>202685</t>
+          <t>206481</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,66%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>251527</t>
+          <t>251653</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>286975</t>
+          <t>286356</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>67,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>76,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>206561</t>
+          <t>205025</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>236686</t>
+          <t>235812</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>68,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>470817</t>
+          <t>467021</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>514074</t>
+          <t>513698</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>69,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,33%</t>
+          <t>76,27%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>93950</t>
+          <t>93008</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>129427</t>
+          <t>129645</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>40,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25636</t>
+          <t>25073</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47356</t>
+          <t>46514</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>126635</t>
+          <t>126082</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>168525</t>
+          <t>165439</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>32,39%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>191780</t>
+          <t>191562</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>227257</t>
+          <t>228199</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>59,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>142232</t>
+          <t>143074</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>163952</t>
+          <t>164515</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>75,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>342270</t>
+          <t>345356</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>384160</t>
+          <t>384713</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>67,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>75,32%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>82707</t>
+          <t>82658</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>112470</t>
+          <t>112860</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>49,51%</t>
+          <t>49,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3009</t>
+          <t>3020</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13540</t>
+          <t>13251</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>88777</t>
+          <t>89005</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>121178</t>
+          <t>122176</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>42,69%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>114675</t>
+          <t>114285</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>144438</t>
+          <t>144487</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>63,59%</t>
+          <t>63,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>45479</t>
+          <t>45768</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>56010</t>
+          <t>55999</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>77,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>164987</t>
+          <t>163989</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>197388</t>
+          <t>197160</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>57,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>68,9%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>46918</t>
+          <t>47313</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>69832</t>
+          <t>69635</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4972</t>
+          <t>4561</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>47189</t>
+          <t>46938</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>71152</t>
+          <t>70362</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>43,26%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>74730</t>
+          <t>74927</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>97644</t>
+          <t>97249</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>51,69%</t>
+          <t>51,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>67,54%</t>
+          <t>67,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>13119</t>
+          <t>13530</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>74,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>91501</t>
+          <t>92291</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>115464</t>
+          <t>115715</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>56,26%</t>
+          <t>56,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>71,14%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>50911</t>
+          <t>52388</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>71663</t>
+          <t>73083</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>59,79%</t>
+          <t>60,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1225</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9326</t>
+          <t>9135</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>65,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>55325</t>
+          <t>55706</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>78151</t>
+          <t>78981</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>59,06%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>48192</t>
+          <t>46772</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>68944</t>
+          <t>67467</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>39,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>57,52%</t>
+          <t>56,29%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>4543</t>
+          <t>4734</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>12644</t>
+          <t>12592</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>55573</t>
+          <t>54743</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>78399</t>
+          <t>78018</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>58,34%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>572225</t>
+          <t>567441</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>650850</t>
+          <t>653171</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>234941</t>
+          <t>234847</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>292311</t>
+          <t>290074</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>820550</t>
+          <t>821881</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>919160</t>
+          <t>921289</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,88%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1070214</t>
+          <t>1067893</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1148839</t>
+          <t>1153623</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>62,18%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>66,75%</t>
+          <t>67,03%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>706053</t>
+          <t>708290</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>763423</t>
+          <t>763517</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>70,72%</t>
+          <t>70,95%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1800267</t>
+          <t>1798138</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1898877</t>
+          <t>1897546</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>66,12%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>69,83%</t>
+          <t>69,78%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>55811</t>
+          <t>57159</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>81084</t>
+          <t>80910</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>51,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>69328</t>
+          <t>70561</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>94491</t>
+          <t>94973</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>61,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>134491</t>
+          <t>134683</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>169599</t>
+          <t>170636</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>54,88%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>74754</t>
+          <t>74928</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>100027</t>
+          <t>98679</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>48,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,19%</t>
+          <t>63,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>60577</t>
+          <t>60095</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>85740</t>
+          <t>84507</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,29%</t>
+          <t>54,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>141307</t>
+          <t>140270</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>176415</t>
+          <t>176223</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>56,68%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>87127</t>
+          <t>88472</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>122886</t>
+          <t>122792</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>65494</t>
+          <t>67339</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>97799</t>
+          <t>99021</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>163098</t>
+          <t>161191</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>211937</t>
+          <t>210587</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,51%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>243139</t>
+          <t>243233</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>278898</t>
+          <t>277553</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,43%</t>
+          <t>66,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>75,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>226296</t>
+          <t>225074</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>258601</t>
+          <t>256756</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,82%</t>
+          <t>69,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>478182</t>
+          <t>479532</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>527021</t>
+          <t>528928</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>69,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>76,64%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>111835</t>
+          <t>111449</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>147939</t>
+          <t>150111</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>78731</t>
+          <t>79031</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>114548</t>
+          <t>114140</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>201462</t>
+          <t>200159</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>254488</t>
+          <t>252949</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>32,62%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>269030</t>
+          <t>266858</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>305134</t>
+          <t>305520</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>64,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>243911</t>
+          <t>244319</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>279728</t>
+          <t>279428</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,04%</t>
+          <t>68,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>77,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>520940</t>
+          <t>522479</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>573966</t>
+          <t>575269</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,18%</t>
+          <t>67,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>74,19%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>136856</t>
+          <t>135761</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>180232</t>
+          <t>179889</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>67560</t>
+          <t>66454</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>101690</t>
+          <t>102741</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>217180</t>
+          <t>217954</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>272785</t>
+          <t>270331</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>35,3%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>262323</t>
+          <t>262666</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>305699</t>
+          <t>306794</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,27%</t>
+          <t>59,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>69,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>221585</t>
+          <t>220534</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>255715</t>
+          <t>256821</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>68,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>79,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>493045</t>
+          <t>495499</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>548650</t>
+          <t>547876</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>64,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>71,54%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>97464</t>
+          <t>95474</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>132478</t>
+          <t>131681</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>45,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8471</t>
+          <t>8423</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23788</t>
+          <t>23447</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>109175</t>
+          <t>109404</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>148819</t>
+          <t>147866</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,32%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>157269</t>
+          <t>158066</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>192283</t>
+          <t>194273</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>54,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>66,36%</t>
+          <t>67,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>93578</t>
+          <t>93919</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>108895</t>
+          <t>108943</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,73%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>258294</t>
+          <t>259247</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>297938</t>
+          <t>297709</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>63,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>73,13%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>71586</t>
+          <t>70788</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>102573</t>
+          <t>101183</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>47,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1706</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10262</t>
+          <t>10790</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>74621</t>
+          <t>75304</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>106848</t>
+          <t>107867</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>44,82%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>109348</t>
+          <t>110738</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>140335</t>
+          <t>141133</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>52,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>66,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>18470</t>
+          <t>17942</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>27026</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>64,28%</t>
+          <t>62,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>133805</t>
+          <t>132786</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>166032</t>
+          <t>165349</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>55,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>68,71%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>61519</t>
+          <t>60973</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>87633</t>
+          <t>87809</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>54,33%</t>
+          <t>54,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>60349</t>
+          <t>61050</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>88211</t>
+          <t>86987</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>50,66%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>73654</t>
+          <t>73478</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>99768</t>
+          <t>100314</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>61,86%</t>
+          <t>62,2%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>83512</t>
+          <t>84736</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>111374</t>
+          <t>110673</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>49,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>64,86%</t>
+          <t>64,45%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>689918</t>
+          <t>691164</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>780342</t>
+          <t>779873</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>331337</t>
+          <t>331478</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>402629</t>
+          <t>400047</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1041138</t>
+          <t>1045128</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1156243</t>
+          <t>1159739</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>34,5%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1264000</t>
+          <t>1264469</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1354424</t>
+          <t>1353178</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>61,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>66,25%</t>
+          <t>66,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>914802</t>
+          <t>917384</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>986094</t>
+          <t>985953</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>69,63%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>74,84%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2205530</t>
+          <t>2202034</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2320635</t>
+          <t>2316645</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>65,5%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>68,91%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>50357</t>
+          <t>49671</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>74699</t>
+          <t>73299</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,3%</t>
+          <t>49,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>48097</t>
+          <t>48376</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>68975</t>
+          <t>69481</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>57,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>104401</t>
+          <t>104246</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>135729</t>
+          <t>136776</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,26%</t>
+          <t>50,65%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>73799</t>
+          <t>75199</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>98141</t>
+          <t>98827</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>50,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,09%</t>
+          <t>66,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>52554</t>
+          <t>52048</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>73432</t>
+          <t>73153</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,42%</t>
+          <t>60,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>134299</t>
+          <t>133252</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>165627</t>
+          <t>165782</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,74%</t>
+          <t>49,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>61,39%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>78833</t>
+          <t>79179</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>111537</t>
+          <t>112583</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>69223</t>
+          <t>69784</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>98323</t>
+          <t>98817</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>155455</t>
+          <t>156795</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>198863</t>
+          <t>201259</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>35,54%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>192110</t>
+          <t>191064</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>224814</t>
+          <t>224468</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,27%</t>
+          <t>62,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,04%</t>
+          <t>73,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>164364</t>
+          <t>163870</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>193464</t>
+          <t>192903</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>62,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>367470</t>
+          <t>365074</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>410878</t>
+          <t>409538</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,89%</t>
+          <t>64,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>72,31%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>85698</t>
+          <t>86551</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>122651</t>
+          <t>120423</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>63748</t>
+          <t>63691</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>95719</t>
+          <t>93286</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>159782</t>
+          <t>161458</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>203993</t>
+          <t>204642</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>32,02%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>213597</t>
+          <t>215825</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>250550</t>
+          <t>249697</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,52%</t>
+          <t>64,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>207102</t>
+          <t>209535</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>239073</t>
+          <t>239130</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>69,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>435076</t>
+          <t>434427</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>479287</t>
+          <t>477611</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>74,74%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>114637</t>
+          <t>115496</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>154698</t>
+          <t>153865</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>47837</t>
+          <t>47093</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>76644</t>
+          <t>74574</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>173098</t>
+          <t>171166</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>220515</t>
+          <t>221943</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,69%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>230673</t>
+          <t>231506</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>270734</t>
+          <t>269875</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,86%</t>
+          <t>60,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,25%</t>
+          <t>70,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>238423</t>
+          <t>240493</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>267230</t>
+          <t>267974</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>76,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>479923</t>
+          <t>478495</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>527340</t>
+          <t>529272</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,52%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>75,56%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>92365</t>
+          <t>93666</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>126889</t>
+          <t>129522</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,32%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26258</t>
+          <t>25801</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>50127</t>
+          <t>49490</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>123538</t>
+          <t>126914</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>167826</t>
+          <t>168272</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>37,0%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>153075</t>
+          <t>150442</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>187599</t>
+          <t>186298</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>53,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>66,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>124672</t>
+          <t>125309</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>148541</t>
+          <t>148998</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>71,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>286936</t>
+          <t>286490</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>331224</t>
+          <t>327848</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,1%</t>
+          <t>63,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>72,09%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>65148</t>
+          <t>64405</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>94139</t>
+          <t>92184</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>49,95%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1039</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9448</t>
+          <t>9379</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8461,7 +8461,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>67496</t>
+          <t>66420</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>97599</t>
+          <t>98075</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>40,68%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>90403</t>
+          <t>92358</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>119394</t>
+          <t>120137</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>50,05%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>64,7%</t>
+          <t>65,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>47104</t>
+          <t>47173</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>55513</t>
+          <t>55512</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,7 +8569,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>143496</t>
+          <t>143020</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>173599</t>
+          <t>174675</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>72,45%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>47471</t>
+          <t>47376</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>69328</t>
+          <t>67545</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>53,1%</t>
+          <t>51,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>48252</t>
+          <t>46741</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>69431</t>
+          <t>69119</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>49,03%</t>
+          <t>48,81%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>61241</t>
+          <t>63024</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>83098</t>
+          <t>83193</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>63,64%</t>
+          <t>63,72%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>72183</t>
+          <t>72495</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>93362</t>
+          <t>94873</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>50,97%</t>
+          <t>51,19%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>66,99%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>598347</t>
+          <t>596422</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>681670</t>
+          <t>678993</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>291263</t>
+          <t>295955</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>356031</t>
+          <t>357459</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>904954</t>
+          <t>908851</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1013420</t>
+          <t>1015207</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>33,69%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1087169</t>
+          <t>1089846</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1170492</t>
+          <t>1172417</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>61,61%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>66,17%</t>
+          <t>66,28%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>888469</t>
+          <t>887041</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>953237</t>
+          <t>948545</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>71,39%</t>
+          <t>71,28%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1999919</t>
+          <t>1998132</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2108385</t>
+          <t>2104488</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>66,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>69,84%</t>
         </is>
       </c>
     </row>
@@ -9665,32 +9665,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>38550</t>
+          <t>35492</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20598</t>
+          <t>20984</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>54966</t>
+          <t>52406</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>53,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>26355</t>
+          <t>26889</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15682</t>
+          <t>16330</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37720</t>
+          <t>40215</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>64905</t>
+          <t>62381</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>47052</t>
+          <t>44416</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>86894</t>
+          <t>85345</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,45%</t>
+          <t>46,15%</t>
         </is>
       </c>
     </row>
@@ -9778,32 +9778,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>59081</t>
+          <t>62282</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42665</t>
+          <t>45368</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>77033</t>
+          <t>76790</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>60,51%</t>
+          <t>63,7%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>46,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,9%</t>
+          <t>78,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>51721</t>
+          <t>60266</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40356</t>
+          <t>46940</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>62394</t>
+          <t>70825</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>66,25%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>51,69%</t>
+          <t>53,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>81,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>110803</t>
+          <t>122548</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>88814</t>
+          <t>99584</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>128656</t>
+          <t>140513</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>66,27%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>50,55%</t>
+          <t>53,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>75,98%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>97631</t>
+          <t>97774</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>97631</t>
+          <t>97774</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>97631</t>
+          <t>97774</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>78076</t>
+          <t>87155</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>78076</t>
+          <t>87155</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>78076</t>
+          <t>87155</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>175708</t>
+          <t>184929</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>175708</t>
+          <t>184929</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>175708</t>
+          <t>184929</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>48471</t>
+          <t>53840</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35044</t>
+          <t>39619</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>64879</t>
+          <t>69003</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>37217</t>
+          <t>38558</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27465</t>
+          <t>28603</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49041</t>
+          <t>51033</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>85688</t>
+          <t>92398</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>68767</t>
+          <t>72322</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>104115</t>
+          <t>111155</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>32,36%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>119215</t>
+          <t>133510</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>102807</t>
+          <t>118347</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>132642</t>
+          <t>147731</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>71,09%</t>
+          <t>71,26%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>63,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>108252</t>
+          <t>117549</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>96428</t>
+          <t>105074</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>118004</t>
+          <t>127504</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,29%</t>
+          <t>67,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>227466</t>
+          <t>251059</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>209039</t>
+          <t>232302</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>244387</t>
+          <t>271135</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>73,1%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,75%</t>
+          <t>67,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>78,94%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>167686</t>
+          <t>187350</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>167686</t>
+          <t>187350</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>167686</t>
+          <t>187350</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>145469</t>
+          <t>156107</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>145469</t>
+          <t>156107</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>145469</t>
+          <t>156107</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>313154</t>
+          <t>343457</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>313154</t>
+          <t>343457</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>313154</t>
+          <t>343457</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>59727</t>
+          <t>64742</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>46702</t>
+          <t>50923</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>72553</t>
+          <t>79632</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>40007</t>
+          <t>42273</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31452</t>
+          <t>33213</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49016</t>
+          <t>52506</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>99734</t>
+          <t>107015</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>84913</t>
+          <t>90377</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>117586</t>
+          <t>124957</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>30,28%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>129394</t>
+          <t>147226</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>116568</t>
+          <t>132336</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>142419</t>
+          <t>161045</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>68,42%</t>
+          <t>69,46%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,64%</t>
+          <t>62,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>146505</t>
+          <t>158472</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>137496</t>
+          <t>148239</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>155060</t>
+          <t>167532</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>275899</t>
+          <t>305697</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>258047</t>
+          <t>287755</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>290720</t>
+          <t>322335</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>73,45%</t>
+          <t>74,07%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>69,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>78,1%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>189121</t>
+          <t>211968</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>189121</t>
+          <t>211968</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>189121</t>
+          <t>211968</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>186512</t>
+          <t>200745</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>186512</t>
+          <t>200745</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>186512</t>
+          <t>200745</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>375633</t>
+          <t>412712</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>375633</t>
+          <t>412712</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>375633</t>
+          <t>412712</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>80135</t>
+          <t>87722</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24159</t>
+          <t>72157</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>154645</t>
+          <t>106111</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>55453</t>
+          <t>57851</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>45504</t>
+          <t>47520</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66152</t>
+          <t>68762</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>135588</t>
+          <t>145573</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>57907</t>
+          <t>127510</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>205247</t>
+          <t>165792</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>28,99%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>451726</t>
+          <t>221013</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>377216</t>
+          <t>202624</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>507702</t>
+          <t>236578</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>71,59%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,92%</t>
+          <t>65,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>76,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>190956</t>
+          <t>205369</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>180257</t>
+          <t>194458</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>200905</t>
+          <t>215700</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>73,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>642682</t>
+          <t>426383</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>573023</t>
+          <t>406164</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>720363</t>
+          <t>444446</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>74,55%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>71,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>77,71%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>531861</t>
+          <t>308735</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>531861</t>
+          <t>308735</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>531861</t>
+          <t>308735</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>246409</t>
+          <t>263220</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>246409</t>
+          <t>263220</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>246409</t>
+          <t>263220</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>778270</t>
+          <t>571956</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>778270</t>
+          <t>571956</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>778270</t>
+          <t>571956</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>118469</t>
+          <t>124230</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>103708</t>
+          <t>106933</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>136371</t>
+          <t>141357</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,43%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>51959</t>
+          <t>55521</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>44281</t>
+          <t>46282</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>62845</t>
+          <t>66269</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>170428</t>
+          <t>179751</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>153306</t>
+          <t>158022</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>190154</t>
+          <t>200653</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>34,84%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>210662</t>
+          <t>227373</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>192760</t>
+          <t>210246</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>225423</t>
+          <t>244670</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>64,01%</t>
+          <t>64,67%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>58,57%</t>
+          <t>59,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>69,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>151848</t>
+          <t>168721</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>140962</t>
+          <t>157973</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>159526</t>
+          <t>177960</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>75,24%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>70,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>362510</t>
+          <t>396095</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>342784</t>
+          <t>375193</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>379632</t>
+          <t>417824</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>68,02%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,32%</t>
+          <t>65,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>72,56%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>329131</t>
+          <t>351603</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>329131</t>
+          <t>351603</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>329131</t>
+          <t>351603</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>203807</t>
+          <t>224242</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>203807</t>
+          <t>224242</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>203807</t>
+          <t>224242</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>532938</t>
+          <t>575846</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>532938</t>
+          <t>575846</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>532938</t>
+          <t>575846</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>84706</t>
+          <t>90993</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>73478</t>
+          <t>76422</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>96791</t>
+          <t>102497</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>42,31%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>20749</t>
+          <t>23216</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15354</t>
+          <t>17488</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26674</t>
+          <t>29586</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>105455</t>
+          <t>114209</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>92329</t>
+          <t>100444</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>118550</t>
+          <t>129059</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>37,73%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>135843</t>
+          <t>151276</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>123758</t>
+          <t>139772</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>147071</t>
+          <t>165847</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>61,59%</t>
+          <t>62,44%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>56,11%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>68,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>70414</t>
+          <t>76598</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>64489</t>
+          <t>70228</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>75809</t>
+          <t>82326</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>77,24%</t>
+          <t>76,74%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,74%</t>
+          <t>70,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>206256</t>
+          <t>227873</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>193161</t>
+          <t>213023</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>219382</t>
+          <t>241638</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>66,17%</t>
+          <t>66,61%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>62,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>70,64%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>220549</t>
+          <t>242269</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>220549</t>
+          <t>242269</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>220549</t>
+          <t>242269</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>91163</t>
+          <t>99814</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>91163</t>
+          <t>99814</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>91163</t>
+          <t>99814</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>311711</t>
+          <t>342082</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>311711</t>
+          <t>342082</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>311711</t>
+          <t>342082</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>57911</t>
+          <t>61987</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>48906</t>
+          <t>51476</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>67174</t>
+          <t>72821</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>43,33%</t>
+          <t>42,24%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>50,26%</t>
+          <t>49,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>3320</t>
+          <t>3554</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1163</t>
+          <t>1472</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6593</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>61231</t>
+          <t>65540</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>52219</t>
+          <t>56085</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>71545</t>
+          <t>76357</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>44,55%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>75730</t>
+          <t>84768</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>66467</t>
+          <t>73934</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>84735</t>
+          <t>95279</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>56,67%</t>
+          <t>57,76%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>49,74%</t>
+          <t>50,38%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>63,4%</t>
+          <t>64,92%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>18955</t>
+          <t>21077</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>15682</t>
+          <t>17889</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>21112</t>
+          <t>23159</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>72,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>94685</t>
+          <t>105846</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>84371</t>
+          <t>95029</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>103697</t>
+          <t>115301</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>60,73%</t>
+          <t>61,76%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>55,45%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>67,28%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>133641</t>
+          <t>146755</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>133641</t>
+          <t>146755</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>133641</t>
+          <t>146755</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>22275</t>
+          <t>24631</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>22275</t>
+          <t>24631</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>22275</t>
+          <t>24631</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>155916</t>
+          <t>171386</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>155916</t>
+          <t>171386</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>155916</t>
+          <t>171386</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>487969</t>
+          <t>519004</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>296898</t>
+          <t>480345</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>587979</t>
+          <t>557676</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>235060</t>
+          <t>247863</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>210736</t>
+          <t>223224</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>259962</t>
+          <t>273858</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>723029</t>
+          <t>766867</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>509845</t>
+          <t>720426</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>811062</t>
+          <t>809577</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>31,11%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1181651</t>
+          <t>1027450</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1081641</t>
+          <t>988778</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1372722</t>
+          <t>1066109</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>66,44%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>64,78%</t>
+          <t>63,94%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>68,94%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>738651</t>
+          <t>808051</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>713749</t>
+          <t>782056</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>762975</t>
+          <t>832690</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>73,3%</t>
+          <t>74,06%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>78,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1920302</t>
+          <t>1835501</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1832269</t>
+          <t>1792791</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2133486</t>
+          <t>1881942</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>70,53%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>69,32%</t>
+          <t>68,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>72,32%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1669620</t>
+          <t>1546454</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1669620</t>
+          <t>1546454</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1669620</t>
+          <t>1546454</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>973711</t>
+          <t>1055914</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>973711</t>
+          <t>1055914</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>973711</t>
+          <t>1055914</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2643331</t>
+          <t>2602368</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2643331</t>
+          <t>2602368</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2643331</t>
+          <t>2602368</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
